--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0083.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0083.xlsx
@@ -22452,7 +22452,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Vào Dòng Hắc Triều {Male=hắn;Female=cô ta} đã biến mất. Tâm trí ta tan vỡ, hy vọng giờ đã tiêu tan.</t>
+          <t>Vào Dòng Hắc Triều {Male=he's;Female=she's} đã biến mất. Tâm trí ta tan vỡ, hy vọng giờ đã tiêu tan.</t>
         </is>
       </c>
     </row>
@@ -22777,7 +22777,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Vung cao chiếc đèn lồng, {Male=hắn;Female=nàng} đã xua tan Bóng Tối. Đêm dài của Rinascita, từ đây kết thúc!</t>
+          <t>Vung cao chiếc đèn lồng, {Male=he;Female=she} đã xua tan Bóng Tối. Đêm dài của Rinascita, từ đây kết thúc!</t>
         </is>
       </c>
     </row>
@@ -24012,7 +24012,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Nhưng nếu hắn không có ở đây, vậy thì ta sẽ đi tìm "Thánh Nữ" ấy... hoặc {PlayerName}.</t>
+          <t>Nhưng nếu hắn không có ở đây, vậy thì tao sẽ đi tìm "Thánh Nữ" ấy... hoặc {PlayerName}.</t>
         </is>
       </c>
     </row>
@@ -24987,7 +24987,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Để ta xử lý việc này.</t>
+          <t>Để tao xử lý việc này.</t>
         </is>
       </c>
     </row>
@@ -25377,7 +25377,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Đưa cái này ra khỏi đầu ta!</t>
+          <t>Đưa cái này ra khỏi đầu tao!</t>
         </is>
       </c>
     </row>
@@ -29342,7 +29342,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Cartethyia, Cộng Hưởng Giả của cả Sentinel và Threnodian.</t>
+          <t>Cartethyia, Resonator của cả Sentinel và Threnodian.</t>
         </is>
       </c>
     </row>
@@ -31227,7 +31227,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Cậu hứa thật chứ?</t>
+          <t>Mày hứa thật chứ?</t>
         </is>
       </c>
     </row>
@@ -32267,7 +32267,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Ủa?</t>
+          <t>Ờ?</t>
         </is>
       </c>
     </row>
@@ -33047,7 +33047,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Hắn làm việc cẩu thả ở Jinzhou và phải chịu trách nhiệm cho những sai lầm của chính mình. Ta sẽ không can thiệp vào cách ngươi xử lý hắn.</t>
+          <t>Hắn làm việc cẩu thả ở Jinzhou và phải chịu trách nhiệm cho những sai lầm của chính mình. Tao sẽ không can thiệp vào cách mày xử lý hắn.</t>
         </is>
       </c>
     </row>
